--- a/data/Employee_Master.xlsx
+++ b/data/Employee_Master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/FB-Sales/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/F&amp;B Sales Dashboard - Project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="19" documentId="8_{435EB669-0B53-404B-9887-A50634BD41E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{648DB516-1579-403F-8846-E935E062E20D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B76173A0-443A-4532-A0AF-4EB7DE1D271E}"/>
+    <workbookView xWindow="8500" yWindow="4120" windowWidth="11760" windowHeight="6160" xr2:uid="{B76173A0-443A-4532-A0AF-4EB7DE1D271E}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee_Master_tbl" sheetId="1" r:id="rId1"/>
